--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,1694 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126595108</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>701841</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360189</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126595132</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101431</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>701900</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126595137</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>701855</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360068</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>40 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126595125</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98389</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>702016</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6360042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126595117</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702024</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6360122</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126595112</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98389</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701848</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6360188</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126595148</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701778</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359998</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126595142</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701807</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359985</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126595122</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701998</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6360055</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126595124</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>702001</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6360045</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126595138</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701837</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6360008</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>40 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126595184</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>702020</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6360085</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126595147</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>701777</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6360000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126595113</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103814</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>701991</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6360183</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126595119</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102494</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>702037</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6360098</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126595108</v>
       </c>
       <c r="B7" t="n">
-        <v>106654</v>
+        <v>106729</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126595132</v>
       </c>
       <c r="B8" t="n">
-        <v>101431</v>
+        <v>101506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>126595137</v>
       </c>
       <c r="B9" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>126595125</v>
       </c>
       <c r="B10" t="n">
-        <v>98389</v>
+        <v>98464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,27 +1697,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126595117</v>
+        <v>126595112</v>
       </c>
       <c r="B11" t="n">
-        <v>106654</v>
+        <v>98464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,20 +1725,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702024</v>
+        <v>701848</v>
       </c>
       <c r="R11" t="n">
-        <v>6360122</v>
+        <v>6360188</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1790,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1799,57 +1808,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126595148</v>
+        <v>126595117</v>
       </c>
       <c r="B12" t="n">
-        <v>102494</v>
+        <v>106729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701778</v>
+        <v>702024</v>
       </c>
       <c r="R12" t="n">
-        <v>6359998</v>
+        <v>6360122</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,11 +1881,6 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1897,7 +1892,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1915,32 +1910,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126595112</v>
+        <v>126595148</v>
       </c>
       <c r="B13" t="n">
-        <v>98389</v>
+        <v>102569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1959,13 +1954,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701848</v>
+        <v>701778</v>
       </c>
       <c r="R13" t="n">
-        <v>6360188</v>
+        <v>6359998</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1990,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2029,7 @@
         <v>126595122</v>
       </c>
       <c r="B14" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126595142</v>
       </c>
       <c r="B15" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>126595124</v>
       </c>
       <c r="B16" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>126595138</v>
       </c>
       <c r="B17" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>126595147</v>
       </c>
       <c r="B19" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126595113</v>
       </c>
       <c r="B20" t="n">
-        <v>103814</v>
+        <v>103889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126595119</v>
       </c>
       <c r="B21" t="n">
-        <v>102494</v>
+        <v>102569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126595108</v>
       </c>
       <c r="B7" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126595132</v>
       </c>
       <c r="B8" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>126595137</v>
       </c>
       <c r="B9" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>126595125</v>
       </c>
       <c r="B10" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,27 +1697,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126595112</v>
+        <v>126595117</v>
       </c>
       <c r="B11" t="n">
-        <v>98464</v>
+        <v>106735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,29 +1725,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701848</v>
+        <v>702024</v>
       </c>
       <c r="R11" t="n">
-        <v>6360188</v>
+        <v>6360122</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,7 +1781,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1808,27 +1799,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126595117</v>
+        <v>126595112</v>
       </c>
       <c r="B12" t="n">
-        <v>106729</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1836,20 +1827,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702024</v>
+        <v>701848</v>
       </c>
       <c r="R12" t="n">
-        <v>6360122</v>
+        <v>6360188</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
         <v>126595148</v>
       </c>
       <c r="B13" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126595122</v>
+        <v>126595142</v>
       </c>
       <c r="B14" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701998</v>
+        <v>701807</v>
       </c>
       <c r="R14" t="n">
-        <v>6360055</v>
+        <v>6359985</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126595142</v>
+        <v>126595122</v>
       </c>
       <c r="B15" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701807</v>
+        <v>701998</v>
       </c>
       <c r="R15" t="n">
-        <v>6359985</v>
+        <v>6360055</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,7 +2261,7 @@
         <v>126595124</v>
       </c>
       <c r="B16" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>126595138</v>
       </c>
       <c r="B17" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>126595147</v>
       </c>
       <c r="B19" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126595113</v>
       </c>
       <c r="B20" t="n">
-        <v>103889</v>
+        <v>103895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126595119</v>
       </c>
       <c r="B21" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -1697,48 +1697,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126595117</v>
+        <v>126595148</v>
       </c>
       <c r="B11" t="n">
-        <v>106735</v>
+        <v>102575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702024</v>
+        <v>701778</v>
       </c>
       <c r="R11" t="n">
-        <v>6360122</v>
+        <v>6359998</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,6 +1779,11 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1781,7 +1795,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1910,57 +1924,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126595148</v>
+        <v>126595117</v>
       </c>
       <c r="B13" t="n">
-        <v>102575</v>
+        <v>106735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701778</v>
+        <v>702024</v>
       </c>
       <c r="R13" t="n">
-        <v>6359998</v>
+        <v>6360122</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,11 +1997,6 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>126595108</v>
       </c>
       <c r="B7" t="n">
-        <v>106735</v>
+        <v>106729</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126595132</v>
       </c>
       <c r="B8" t="n">
-        <v>101512</v>
+        <v>101506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>126595137</v>
       </c>
       <c r="B9" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>126595125</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,32 +1697,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126595148</v>
+        <v>126595112</v>
       </c>
       <c r="B11" t="n">
-        <v>102575</v>
+        <v>98464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6037533</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701778</v>
+        <v>701848</v>
       </c>
       <c r="R11" t="n">
-        <v>6359998</v>
+        <v>6360188</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,11 +1777,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,27 +1808,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126595112</v>
+        <v>126595117</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>106729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1841,29 +1836,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701848</v>
+        <v>702024</v>
       </c>
       <c r="R12" t="n">
-        <v>6360188</v>
+        <v>6360122</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,7 +1892,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, myrkulle i glänta.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1924,48 +1910,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126595117</v>
+        <v>126595148</v>
       </c>
       <c r="B13" t="n">
-        <v>106735</v>
+        <v>102569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702024</v>
+        <v>701778</v>
       </c>
       <c r="R13" t="n">
-        <v>6360122</v>
+        <v>6359998</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,6 +1992,11 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, myrkulle i glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126595142</v>
+        <v>126595122</v>
       </c>
       <c r="B14" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701807</v>
+        <v>701998</v>
       </c>
       <c r="R14" t="n">
-        <v>6359985</v>
+        <v>6360055</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126595122</v>
+        <v>126595142</v>
       </c>
       <c r="B15" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701998</v>
+        <v>701807</v>
       </c>
       <c r="R15" t="n">
-        <v>6360055</v>
+        <v>6359985</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,7 +2261,7 @@
         <v>126595124</v>
       </c>
       <c r="B16" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>126595138</v>
       </c>
       <c r="B17" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>126595147</v>
       </c>
       <c r="B19" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126595113</v>
       </c>
       <c r="B20" t="n">
-        <v>103895</v>
+        <v>103889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126595119</v>
       </c>
       <c r="B21" t="n">
-        <v>102575</v>
+        <v>102569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97356373</v>
+        <v>97356370</v>
       </c>
       <c r="B2" t="n">
-        <v>85244</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6037417</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulfotad denisespindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A.Ortega, Vila &amp; Fern.-Brime</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701964.8968811589</v>
+        <v>701978</v>
       </c>
       <c r="R2" t="n">
-        <v>6359889.38990856</v>
+        <v>6360006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97356370</v>
+        <v>97356372</v>
       </c>
       <c r="B3" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701978.6259489029</v>
+        <v>701735</v>
       </c>
       <c r="R3" t="n">
-        <v>6360006.302014311</v>
+        <v>6360028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2021-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97356372</v>
+        <v>97356365</v>
       </c>
       <c r="B4" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701734.8950424142</v>
+        <v>701936</v>
       </c>
       <c r="R4" t="n">
-        <v>6360027.794313481</v>
+        <v>6360010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2021-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,58 +978,67 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97357029</v>
+        <v>129317244</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ase, Stangsmyr V, Gtl</t>
+          <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701734.8950424142</v>
+        <v>702020</v>
       </c>
       <c r="R5" t="n">
-        <v>6360027.794313481</v>
+        <v>6360085</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,34 +1076,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97356365</v>
+        <v>97357029</v>
       </c>
       <c r="B6" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,26 +1110,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701936.1849351204</v>
+        <v>701735</v>
       </c>
       <c r="R6" t="n">
-        <v>6360010.153706717</v>
+        <v>6360028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1172,9 @@
           <t>2021-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,27 +1202,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126595108</v>
+        <v>129317281</v>
       </c>
       <c r="B7" t="n">
-        <v>106735</v>
+        <v>99147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1285,20 +1230,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701841</v>
+        <v>701848</v>
       </c>
       <c r="R7" t="n">
-        <v>6360189</v>
+        <v>6360188</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,44 +1306,44 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126595132</v>
+        <v>129317294</v>
       </c>
       <c r="B8" t="n">
-        <v>101512</v>
+        <v>99147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701900</v>
+        <v>702016</v>
       </c>
       <c r="R8" t="n">
-        <v>6360049</v>
+        <v>6360042</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1463,64 +1417,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126595137</v>
+        <v>129317282</v>
       </c>
       <c r="B9" t="n">
-        <v>102575</v>
+        <v>104639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6037533</v>
+        <v>220164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701855</v>
+        <v>701991</v>
       </c>
       <c r="R9" t="n">
-        <v>6360068</v>
+        <v>6360183</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,44 +1519,44 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126595125</v>
+        <v>129317299</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>102224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>221223</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1630,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702016</v>
+        <v>701900</v>
       </c>
       <c r="R10" t="n">
-        <v>6360042</v>
+        <v>6360049</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,64 +1630,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126595148</v>
+        <v>120308076</v>
       </c>
       <c r="B11" t="n">
-        <v>102575</v>
+        <v>107517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Linde Rangsarve 1:4 (3), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701778</v>
+        <v>701638</v>
       </c>
       <c r="R11" t="n">
-        <v>6359998</v>
+        <v>6360226</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,17 +1702,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1721,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta i gränsgata.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1813,27 +1739,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126595112</v>
+        <v>129317278</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>107516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1841,29 +1767,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701848</v>
+        <v>701841</v>
       </c>
       <c r="R12" t="n">
-        <v>6360188</v>
+        <v>6360189</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,17 +1834,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126595117</v>
+        <v>129317285</v>
       </c>
       <c r="B13" t="n">
-        <v>106735</v>
+        <v>107516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,64 +1936,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126595142</v>
+        <v>129317277</v>
       </c>
       <c r="B14" t="n">
-        <v>102575</v>
+        <v>102559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>222133</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701807</v>
+        <v>701841</v>
       </c>
       <c r="R14" t="n">
-        <v>6359985</v>
+        <v>6360189</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,11 +2014,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,64 +2038,58 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126595122</v>
+        <v>97356373</v>
       </c>
       <c r="B15" t="n">
-        <v>102575</v>
+        <v>87312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>6037417</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ase 1:24 (4), Gtl</t>
+          <t>Ase, Stangsmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701998</v>
+        <v>701965</v>
       </c>
       <c r="R15" t="n">
-        <v>6360055</v>
+        <v>6359889</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,17 +2113,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>50 cm hög, steil.</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,33 +2127,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126595124</v>
+        <v>129317287</v>
       </c>
       <c r="B16" t="n">
-        <v>102575</v>
+        <v>103305</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2302,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702001</v>
+        <v>702037</v>
       </c>
       <c r="R16" t="n">
-        <v>6360045</v>
+        <v>6360098</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2342,7 +2230,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>30 cm hög, steil.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,17 +2255,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126595138</v>
+        <v>129317290</v>
       </c>
       <c r="B17" t="n">
-        <v>102575</v>
+        <v>103305</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701837</v>
+        <v>701998</v>
       </c>
       <c r="R17" t="n">
-        <v>6360008</v>
+        <v>6360055</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2458,7 +2346,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>40 cm hög, steil.</t>
+          <t>50 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,39 +2371,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126595184</v>
+        <v>129317293</v>
       </c>
       <c r="B18" t="n">
-        <v>43228</v>
+        <v>103305</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2525,17 +2413,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2544,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702020</v>
+        <v>702001</v>
       </c>
       <c r="R18" t="n">
-        <v>6360085</v>
+        <v>6360045</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2582,6 +2460,11 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>30 cm hög, steil.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2593,7 +2476,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2604,17 +2487,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126595147</v>
+        <v>129317303</v>
       </c>
       <c r="B19" t="n">
-        <v>102575</v>
+        <v>103305</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,13 +2538,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701777</v>
+        <v>701855</v>
       </c>
       <c r="R19" t="n">
-        <v>6360000</v>
+        <v>6360068</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2695,7 +2578,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,55 +2603,64 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126595113</v>
+        <v>129317304</v>
       </c>
       <c r="B20" t="n">
-        <v>103895</v>
+        <v>103305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220164</v>
+        <v>6037533</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ase 1:24 (4), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701991</v>
+        <v>701837</v>
       </c>
       <c r="R20" t="n">
-        <v>6360183</v>
+        <v>6360008</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2798,6 +2690,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>40 cm hög, steil.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,17 +2719,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126595119</v>
+        <v>129317307</v>
       </c>
       <c r="B21" t="n">
-        <v>102575</v>
+        <v>103305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,13 +2770,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702037</v>
+        <v>701807</v>
       </c>
       <c r="R21" t="n">
-        <v>6360098</v>
+        <v>6359985</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2913,7 +2810,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50 cm hög, steil.</t>
+          <t>4 m hög, knäckt på mitten, angripen, steril. 2 stammar 1,5 cm + 5 cmi diameter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,10 +2835,242 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129317312</v>
+      </c>
+      <c r="B22" t="n">
+        <v>103305</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>701777</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6360000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1, 2 m hög, steril. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129317313</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103305</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ase 1:24 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>701778</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359998</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>50 cm hög, steil.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Bengt Carlsson, Brita Svensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -2149,7 +2149,7 @@
         <v>129317287</v>
       </c>
       <c r="B16" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>129317290</v>
       </c>
       <c r="B17" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>129317293</v>
       </c>
       <c r="B18" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129317303</v>
       </c>
       <c r="B19" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>129317304</v>
       </c>
       <c r="B20" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129317307</v>
       </c>
       <c r="B21" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>129317312</v>
       </c>
       <c r="B22" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>129317313</v>
       </c>
       <c r="B23" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 584-2023 artfynd.xlsx
+++ b/artfynd/A 584-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97357029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317281</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317294</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317299</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308076</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317278</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317285</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317277</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356373</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317287</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2375,6 +2455,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317290</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317293</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2607,6 +2697,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317303</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317304</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317307</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317312</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3071,8 +3181,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>